--- a/Imminent_Deadline_Risk_Predictor.xlsx
+++ b/Imminent_Deadline_Risk_Predictor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VINTAGE\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VINTAGE\Documents\Excel Project Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{104AA084-EF4B-4590-9494-C2D3B6D571CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6215EF-3844-4A0B-A114-CDAEA3FA6BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E62696C5-1BAC-44C5-99AC-3711DFF68A52}"/>
   </bookViews>
@@ -471,7 +471,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,15 +495,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="20"/>
+      <sz val="32"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -524,7 +531,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor rgb="FF6666FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8585FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,47 +561,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="14">
     <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
         <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -626,41 +669,131 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF8585FF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF6666FF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF8585FF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD6D6"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF6666FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF8585FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF6666FF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -668,6 +801,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9900"/>
+      <color rgb="FF0000C4"/>
+      <color rgb="FF8585FF"/>
+      <color rgb="FF6666FF"/>
       <color rgb="FFE2EFDA"/>
       <color rgb="FF375623"/>
       <color rgb="FFFFF2CC"/>
@@ -691,21 +828,21 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3BE46E9B-06FB-454D-ACA4-B34C0F481334}" name="Table8" displayName="Table8" ref="A7:G131" totalsRowShown="0">
   <autoFilter ref="A7:G131" xr:uid="{3BE46E9B-06FB-454D-ACA4-B34C0F481334}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{30CF7C92-2164-4D23-8618-450131DC1038}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00FB6388-A425-4FEE-AFC2-15C88454A372}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{52FFA585-E538-4A3E-9ABD-7DD626CBE20B}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{D18E9616-3B0A-4B40-8EB7-B21BA28574AE}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{24134597-A2E8-4177-94B7-3B6A4CCF8863}" name="Column5" dataDxfId="1" dataCellStyle="Percent">
+    <tableColumn id="1" xr3:uid="{30CF7C92-2164-4D23-8618-450131DC1038}" name="Column1" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00FB6388-A425-4FEE-AFC2-15C88454A372}" name="Column2" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{52FFA585-E538-4A3E-9ABD-7DD626CBE20B}" name="Column3" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{D18E9616-3B0A-4B40-8EB7-B21BA28574AE}" name="Column4" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{24134597-A2E8-4177-94B7-3B6A4CCF8863}" name="Column5" dataDxfId="9" dataCellStyle="Percent">
       <calculatedColumnFormula>(C8-B8)/C8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{90D918BD-02FE-49E6-9485-0C75EB913477}" name="Column6" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{90D918BD-02FE-49E6-9485-0C75EB913477}" name="Column6" dataDxfId="8">
       <calculatedColumnFormula>(E8/D8)*10</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{7C46C69D-F4CF-4512-B65A-651C23C55A7C}" name="Column7">
       <calculatedColumnFormula>IF(F8&gt;1,"High Risk",IF(F8&gt;0.5,"Medium Risk","Low Risk"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1038,93 +1175,93 @@
     <col min="7" max="7" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="42.6" x14ac:dyDescent="0.85">
+      <c r="A1" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <f>COUNTA(A8:A131)</f>
         <v>124</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="11">
         <f>COUNTIF(G8:G131,"High Risk")</f>
-        <v>48</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="11">
         <f>COUNTIF(G8:G131,"Medium Risk")</f>
         <v>49</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="11">
         <f>COUNTIF(G8:G131,"Low Risk")</f>
-        <v>27</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1152,49 +1289,49 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="8">
         <v>4</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="7">
         <v>10</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="8">
         <v>3</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="10">
         <f>(C8-B8)/C8</f>
         <v>0.6</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="9">
         <f>(E8/D8)*10</f>
         <v>1.9999999999999998</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G8" s="5" t="str">
         <f>IF(F8&gt;1,"High Risk",IF(F8&gt;0.5,"Medium Risk","Low Risk"))</f>
         <v>High Risk</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="8">
         <v>7</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>12</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="8">
         <v>4</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="10">
         <f t="shared" ref="E9:E72" si="0">(C9-B9)/C9</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="9">
         <f t="shared" ref="F9:F72" si="1">(E9/D9)*10</f>
         <v>1.0416666666666667</v>
       </c>
@@ -1204,23 +1341,23 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="8">
         <v>5</v>
       </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="7">
+        <v>9</v>
+      </c>
+      <c r="D10" s="8">
         <v>6</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="10">
         <f t="shared" si="0"/>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="9">
         <f t="shared" si="1"/>
         <v>0.7407407407407407</v>
       </c>
@@ -1230,23 +1367,23 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11">
+      <c r="A11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
         <v>10</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="8">
         <v>2</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="10">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="9">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -1256,23 +1393,23 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="8">
         <v>4</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="7">
         <v>15</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="8">
         <v>10</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="10">
         <f t="shared" si="0"/>
         <v>0.73333333333333328</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="9">
         <f t="shared" si="1"/>
         <v>0.73333333333333339</v>
       </c>
@@ -1282,23 +1419,23 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="8">
         <v>6</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="7">
         <v>8</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="8">
         <v>1</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="10">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="9">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
@@ -1308,23 +1445,23 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="8">
         <v>3</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="7">
         <v>14</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="8">
         <v>8</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="10">
         <f t="shared" si="0"/>
         <v>0.7857142857142857</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="9">
         <f t="shared" si="1"/>
         <v>0.9821428571428571</v>
       </c>
@@ -1334,23 +1471,23 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="8">
         <v>8</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="7">
         <v>11</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="8">
         <v>5</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="10">
         <f t="shared" si="0"/>
         <v>0.27272727272727271</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="9">
         <f t="shared" si="1"/>
         <v>0.54545454545454541</v>
       </c>
@@ -1360,23 +1497,23 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="8">
         <v>10</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="7">
         <v>10</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="8">
         <v>3</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1386,23 +1523,23 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="8">
         <v>5</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="7">
         <v>13</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="8">
         <v>7</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="10">
         <f t="shared" si="0"/>
         <v>0.61538461538461542</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="9">
         <f t="shared" si="1"/>
         <v>0.87912087912087922</v>
       </c>
@@ -1412,23 +1549,23 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="8">
         <v>6</v>
       </c>
-      <c r="C18">
-        <v>9</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="7">
+        <v>9</v>
+      </c>
+      <c r="D18" s="8">
         <v>2</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="10">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="9">
         <f t="shared" si="1"/>
         <v>1.6666666666666665</v>
       </c>
@@ -1438,23 +1575,23 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="8">
         <v>2</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="7">
         <v>16</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="8">
         <v>12</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="10">
         <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="9">
         <f t="shared" si="1"/>
         <v>0.72916666666666674</v>
       </c>
@@ -1464,23 +1601,23 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="8">
         <v>7</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="7">
         <v>10</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="8">
         <v>4</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="10">
         <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="9">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
@@ -1490,23 +1627,23 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B21">
-        <v>9</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="8">
+        <v>9</v>
+      </c>
+      <c r="C21" s="7">
         <v>12</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="8">
         <v>6</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="10">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="9">
         <f t="shared" si="1"/>
         <v>0.41666666666666663</v>
       </c>
@@ -1516,23 +1653,23 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="8">
         <v>4</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="7">
         <v>10</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="8">
         <v>3</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="10">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="9">
         <f t="shared" si="1"/>
         <v>1.9999999999999998</v>
       </c>
@@ -1542,23 +1679,23 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="8">
         <v>6</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="7">
         <v>8</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="8">
         <v>1</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="10">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="9">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
@@ -1568,23 +1705,23 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="8">
         <v>3</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="7">
         <v>11</v>
       </c>
-      <c r="D24">
-        <v>9</v>
-      </c>
-      <c r="E24" s="2">
+      <c r="D24" s="8">
+        <v>9</v>
+      </c>
+      <c r="E24" s="10">
         <f t="shared" si="0"/>
         <v>0.72727272727272729</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="9">
         <f t="shared" si="1"/>
         <v>0.80808080808080818</v>
       </c>
@@ -1594,23 +1731,23 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="8">
         <v>8</v>
       </c>
-      <c r="C25">
-        <v>9</v>
-      </c>
-      <c r="D25">
+      <c r="C25" s="7">
+        <v>9</v>
+      </c>
+      <c r="D25" s="8">
         <v>2</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="10">
         <f t="shared" si="0"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="9">
         <f t="shared" si="1"/>
         <v>0.55555555555555558</v>
       </c>
@@ -1620,23 +1757,23 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="8">
         <v>5</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="7">
         <v>7</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="8">
         <v>1</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="10">
         <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="9">
         <f t="shared" si="1"/>
         <v>2.8571428571428568</v>
       </c>
@@ -1646,23 +1783,23 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="8">
         <v>10</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="7">
         <v>12</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="8">
         <v>5</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="10">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="9">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
@@ -1672,23 +1809,23 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="8">
         <v>2</v>
       </c>
-      <c r="C28">
-        <v>9</v>
-      </c>
-      <c r="D28">
+      <c r="C28" s="7">
+        <v>9</v>
+      </c>
+      <c r="D28" s="8">
         <v>4</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="10">
         <f t="shared" si="0"/>
         <v>0.77777777777777779</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="9">
         <f t="shared" si="1"/>
         <v>1.9444444444444444</v>
       </c>
@@ -1698,23 +1835,23 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="8">
         <v>6</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="7">
         <v>14</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="8">
         <v>7</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="10">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="9">
         <f t="shared" si="1"/>
         <v>0.81632653061224481</v>
       </c>
@@ -1724,23 +1861,23 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="8">
         <v>4</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="7">
         <v>10</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="8">
         <v>2</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="10">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="9">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -1750,23 +1887,23 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B31">
-        <v>9</v>
-      </c>
-      <c r="C31">
-        <v>9</v>
-      </c>
-      <c r="D31">
+      <c r="B31" s="8">
+        <v>9</v>
+      </c>
+      <c r="C31" s="7">
+        <v>9</v>
+      </c>
+      <c r="D31" s="8">
         <v>3</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1776,23 +1913,23 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="8">
         <v>3</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="7">
         <v>8</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="8">
         <v>6</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="10">
         <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="9">
         <f t="shared" si="1"/>
         <v>1.0416666666666667</v>
       </c>
@@ -1802,23 +1939,23 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="8">
         <v>7</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="7">
         <v>10</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="8">
         <v>5</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="10">
         <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="9">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -1828,23 +1965,23 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="8">
         <v>5</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="7">
         <v>12</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="8">
         <v>8</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="10">
         <f t="shared" si="0"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="9">
         <f t="shared" si="1"/>
         <v>0.72916666666666674</v>
       </c>
@@ -1854,23 +1991,23 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="8">
         <v>8</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="7">
         <v>8</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="8">
         <v>1</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1880,23 +2017,23 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="8">
         <v>4</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="7">
         <v>15</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="8">
         <v>10</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="10">
         <f t="shared" si="0"/>
         <v>0.73333333333333328</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="9">
         <f t="shared" si="1"/>
         <v>0.73333333333333339</v>
       </c>
@@ -1906,23 +2043,23 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="8">
         <v>6</v>
       </c>
-      <c r="C37">
-        <v>9</v>
-      </c>
-      <c r="D37">
+      <c r="C37" s="7">
+        <v>9</v>
+      </c>
+      <c r="D37" s="8">
         <v>3</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="10">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="9">
         <f t="shared" si="1"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1932,23 +2069,23 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B38">
-        <v>9</v>
-      </c>
-      <c r="C38">
+      <c r="B38" s="8">
+        <v>9</v>
+      </c>
+      <c r="C38" s="7">
         <v>11</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="8">
         <v>4</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="10">
         <f t="shared" si="0"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="9">
         <f t="shared" si="1"/>
         <v>0.45454545454545459</v>
       </c>
@@ -1958,23 +2095,23 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="8">
         <v>7</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="7">
         <v>7</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="8">
         <v>2</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1984,23 +2121,23 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="8">
         <v>3</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="7">
         <v>10</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="8">
         <v>6</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="10">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="9">
         <f t="shared" si="1"/>
         <v>1.1666666666666665</v>
       </c>
@@ -2010,23 +2147,23 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="8">
         <v>8</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="7">
         <v>13</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="8">
         <v>5</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="10">
         <f t="shared" si="0"/>
         <v>0.38461538461538464</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="9">
         <f t="shared" si="1"/>
         <v>0.76923076923076927</v>
       </c>
@@ -2036,23 +2173,23 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="8">
         <v>5</v>
       </c>
-      <c r="C42">
-        <v>9</v>
-      </c>
-      <c r="D42">
+      <c r="C42" s="7">
+        <v>9</v>
+      </c>
+      <c r="D42" s="8">
         <v>2</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="10">
         <f t="shared" si="0"/>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="9">
         <f t="shared" si="1"/>
         <v>2.2222222222222223</v>
       </c>
@@ -2062,23 +2199,23 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="8">
         <v>10</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="7">
         <v>10</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="8">
         <v>4</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2088,23 +2225,23 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="8">
         <v>4</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="7">
         <v>12</v>
       </c>
-      <c r="D44">
-        <v>9</v>
-      </c>
-      <c r="E44" s="2">
+      <c r="D44" s="8">
+        <v>9</v>
+      </c>
+      <c r="E44" s="10">
         <f t="shared" si="0"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="9">
         <f t="shared" si="1"/>
         <v>0.7407407407407407</v>
       </c>
@@ -2114,23 +2251,23 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="8">
         <v>6</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="7">
         <v>11</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="8">
         <v>3</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="10">
         <f t="shared" si="0"/>
         <v>0.45454545454545453</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="9">
         <f t="shared" si="1"/>
         <v>1.5151515151515151</v>
       </c>
@@ -2140,23 +2277,23 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B46">
-        <v>9</v>
-      </c>
-      <c r="C46">
-        <v>9</v>
-      </c>
-      <c r="D46">
+      <c r="B46" s="8">
+        <v>9</v>
+      </c>
+      <c r="C46" s="7">
+        <v>9</v>
+      </c>
+      <c r="D46" s="8">
         <v>1</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2166,23 +2303,23 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="8">
         <v>3</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="7">
         <v>8</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="8">
         <v>5</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="10">
         <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="9">
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
@@ -2192,23 +2329,23 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="8">
         <v>7</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="7">
         <v>14</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="8">
         <v>6</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="10">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="9">
         <f t="shared" si="1"/>
         <v>0.83333333333333326</v>
       </c>
@@ -2218,23 +2355,23 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="8">
         <v>5</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="7">
         <v>10</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="8">
         <v>2</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="10">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="9">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
@@ -2244,23 +2381,23 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="8">
         <v>8</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="7">
         <v>12</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="8">
         <v>7</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="10">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="9">
         <f t="shared" si="1"/>
         <v>0.47619047619047616</v>
       </c>
@@ -2270,23 +2407,23 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="8">
         <v>2</v>
       </c>
-      <c r="C51">
-        <v>9</v>
-      </c>
-      <c r="D51">
+      <c r="C51" s="7">
+        <v>9</v>
+      </c>
+      <c r="D51" s="8">
         <v>3</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="10">
         <f t="shared" si="0"/>
         <v>0.77777777777777779</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="9">
         <f t="shared" si="1"/>
         <v>2.5925925925925926</v>
       </c>
@@ -2296,23 +2433,23 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="8">
         <v>6</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="7">
         <v>8</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="8">
         <v>1</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="10">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="9">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
@@ -2322,23 +2459,23 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="8">
         <v>4</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="7">
         <v>13</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="8">
         <v>10</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="10">
         <f t="shared" si="0"/>
         <v>0.69230769230769229</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="9">
         <f t="shared" si="1"/>
         <v>0.69230769230769229</v>
       </c>
@@ -2348,23 +2485,23 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B54">
-        <v>9</v>
-      </c>
-      <c r="C54">
+      <c r="B54" s="8">
+        <v>9</v>
+      </c>
+      <c r="C54" s="7">
         <v>10</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="8">
         <v>4</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="10">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="9">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
@@ -2374,23 +2511,23 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="8">
         <v>7</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="7">
         <v>11</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="8">
         <v>5</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="10">
         <f t="shared" si="0"/>
         <v>0.36363636363636365</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="9">
         <f t="shared" si="1"/>
         <v>0.72727272727272729</v>
       </c>
@@ -2400,23 +2537,23 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="8">
         <v>5</v>
       </c>
-      <c r="C56">
-        <v>9</v>
-      </c>
-      <c r="D56">
+      <c r="C56" s="7">
+        <v>9</v>
+      </c>
+      <c r="D56" s="8">
         <v>2</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="10">
         <f t="shared" si="0"/>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="9">
         <f t="shared" si="1"/>
         <v>2.2222222222222223</v>
       </c>
@@ -2426,23 +2563,23 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="8">
         <v>8</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="7">
         <v>10</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="8">
         <v>3</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="10">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="9">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
@@ -2452,23 +2589,23 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="8">
         <v>6</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="7">
         <v>7</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="8">
         <v>1</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="10">
         <f t="shared" si="0"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="9">
         <f t="shared" si="1"/>
         <v>1.4285714285714284</v>
       </c>
@@ -2478,23 +2615,23 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="8">
         <v>3</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="7">
         <v>12</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="8">
         <v>8</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="10">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="9">
         <f t="shared" si="1"/>
         <v>0.9375</v>
       </c>
@@ -2504,23 +2641,23 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B60">
-        <v>9</v>
-      </c>
-      <c r="C60">
-        <v>9</v>
-      </c>
-      <c r="D60">
+      <c r="B60" s="8">
+        <v>9</v>
+      </c>
+      <c r="C60" s="7">
+        <v>9</v>
+      </c>
+      <c r="D60" s="8">
         <v>2</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2530,23 +2667,23 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="8">
         <v>5</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="7">
         <v>10</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="8">
         <v>4</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="10">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="9">
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
@@ -2556,23 +2693,23 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="8">
         <v>7</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="7">
         <v>13</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="8">
         <v>6</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="10">
         <f t="shared" si="0"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="9">
         <f t="shared" si="1"/>
         <v>0.76923076923076927</v>
       </c>
@@ -2582,23 +2719,23 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="8">
         <v>4</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="7">
         <v>8</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="8">
         <v>1</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="10">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="9">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2608,23 +2745,23 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="8">
         <v>10</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="7">
         <v>11</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="8">
         <v>5</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="10">
         <f t="shared" si="0"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="9">
         <f t="shared" si="1"/>
         <v>0.18181818181818182</v>
       </c>
@@ -2634,23 +2771,23 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="8">
         <v>6</v>
       </c>
-      <c r="C65">
-        <v>9</v>
-      </c>
-      <c r="D65">
+      <c r="C65" s="7">
+        <v>9</v>
+      </c>
+      <c r="D65" s="8">
         <v>3</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="10">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="9">
         <f t="shared" si="1"/>
         <v>1.1111111111111112</v>
       </c>
@@ -2660,23 +2797,23 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="8">
         <v>8</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="7">
         <v>12</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="8">
         <v>7</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="10">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="9">
         <f t="shared" si="1"/>
         <v>0.47619047619047616</v>
       </c>
@@ -2686,23 +2823,23 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="8">
         <v>3</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="7">
         <v>10</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="8">
         <v>2</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="10">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="9">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
@@ -2712,23 +2849,23 @@
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="A68" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="8">
         <v>7</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="7">
         <v>8</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="8">
         <v>1</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="10">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="9">
         <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
@@ -2738,23 +2875,23 @@
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="8">
         <v>6</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="7">
         <v>10</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="8">
         <v>4</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="10">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="9">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2764,23 +2901,23 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="8">
         <v>8</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="7">
         <v>12</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="8">
         <v>6</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="10">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="9">
         <f t="shared" si="1"/>
         <v>0.55555555555555558</v>
       </c>
@@ -2790,23 +2927,23 @@
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="8">
         <v>5</v>
       </c>
-      <c r="C71">
-        <v>9</v>
-      </c>
-      <c r="D71">
+      <c r="C71" s="7">
+        <v>9</v>
+      </c>
+      <c r="D71" s="8">
         <v>2</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="10">
         <f t="shared" si="0"/>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="9">
         <f t="shared" si="1"/>
         <v>2.2222222222222223</v>
       </c>
@@ -2816,23 +2953,23 @@
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="8">
         <v>4</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="7">
         <v>11</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="8">
         <v>7</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="10">
         <f t="shared" si="0"/>
         <v>0.63636363636363635</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="9">
         <f t="shared" si="1"/>
         <v>0.90909090909090917</v>
       </c>
@@ -2842,23 +2979,23 @@
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B73">
-        <v>9</v>
-      </c>
-      <c r="C73">
+      <c r="B73" s="8">
+        <v>9</v>
+      </c>
+      <c r="C73" s="7">
         <v>13</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="8">
         <v>3</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="10">
         <f t="shared" ref="E73:E131" si="3">(C73-B73)/C73</f>
         <v>0.30769230769230771</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="9">
         <f t="shared" ref="F73:F131" si="4">(E73/D73)*10</f>
         <v>1.0256410256410258</v>
       </c>
@@ -2868,23 +3005,23 @@
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="8">
         <v>7</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="7">
         <v>10</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="8">
         <v>5</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="10">
         <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="9">
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
@@ -2894,23 +3031,23 @@
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="8">
         <v>3</v>
       </c>
-      <c r="C75">
-        <v>9</v>
-      </c>
-      <c r="D75">
+      <c r="C75" s="7">
+        <v>9</v>
+      </c>
+      <c r="D75" s="8">
         <v>8</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="10">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="9">
         <f t="shared" si="4"/>
         <v>0.83333333333333326</v>
       </c>
@@ -2920,23 +3057,23 @@
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="8">
         <v>6</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="7">
         <v>8</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="8">
         <v>1</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="10">
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="9">
         <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
@@ -2946,23 +3083,23 @@
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="8">
         <v>5</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="7">
         <v>12</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="8">
         <v>6</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="10">
         <f t="shared" si="3"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="9">
         <f t="shared" si="4"/>
         <v>0.97222222222222221</v>
       </c>
@@ -2972,23 +3109,23 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="8">
         <v>8</v>
       </c>
-      <c r="C78">
-        <v>9</v>
-      </c>
-      <c r="D78">
+      <c r="C78" s="7">
+        <v>9</v>
+      </c>
+      <c r="D78" s="8">
         <v>2</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="10">
         <f t="shared" si="3"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="9">
         <f t="shared" si="4"/>
         <v>0.55555555555555558</v>
       </c>
@@ -2998,23 +3135,23 @@
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="A79" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="8">
         <v>4</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="7">
         <v>14</v>
       </c>
-      <c r="D79">
-        <v>9</v>
-      </c>
-      <c r="E79" s="2">
+      <c r="D79" s="8">
+        <v>9</v>
+      </c>
+      <c r="E79" s="10">
         <f t="shared" si="3"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="9">
         <f t="shared" si="4"/>
         <v>0.79365079365079361</v>
       </c>
@@ -3024,23 +3161,23 @@
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="8">
         <v>7</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="7">
         <v>10</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="8">
         <v>3</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="10">
         <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="9">
         <f t="shared" si="4"/>
         <v>0.99999999999999989</v>
       </c>
@@ -3050,23 +3187,23 @@
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B81">
-        <v>9</v>
-      </c>
-      <c r="C81">
+      <c r="B81" s="8">
+        <v>9</v>
+      </c>
+      <c r="C81" s="7">
         <v>11</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="8">
         <v>4</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="10">
         <f t="shared" si="3"/>
         <v>0.18181818181818182</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="9">
         <f t="shared" si="4"/>
         <v>0.45454545454545459</v>
       </c>
@@ -3076,23 +3213,23 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="8">
         <v>5</v>
       </c>
-      <c r="C82">
-        <v>9</v>
-      </c>
-      <c r="D82">
+      <c r="C82" s="7">
+        <v>9</v>
+      </c>
+      <c r="D82" s="8">
         <v>2</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="10">
         <f t="shared" si="3"/>
         <v>0.44444444444444442</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="9">
         <f t="shared" si="4"/>
         <v>2.2222222222222223</v>
       </c>
@@ -3102,23 +3239,23 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="A83" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="8">
         <v>6</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="7">
         <v>13</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="8">
         <v>7</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="10">
         <f t="shared" si="3"/>
         <v>0.53846153846153844</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83" s="9">
         <f t="shared" si="4"/>
         <v>0.76923076923076916</v>
       </c>
@@ -3128,23 +3265,23 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="A84" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="8">
         <v>3</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="7">
         <v>10</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="8">
         <v>5</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="10">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84" s="9">
         <f t="shared" si="4"/>
         <v>1.4</v>
       </c>
@@ -3154,23 +3291,23 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="8">
         <v>8</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="7">
         <v>8</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="8">
         <v>1</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85" s="9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -3180,23 +3317,23 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="8">
         <v>4</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="7">
         <v>12</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="8">
         <v>8</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="10">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86" s="9">
         <f t="shared" si="4"/>
         <v>0.83333333333333326</v>
       </c>
@@ -3206,23 +3343,23 @@
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="8">
         <v>7</v>
       </c>
-      <c r="C87">
-        <v>9</v>
-      </c>
-      <c r="D87">
+      <c r="C87" s="7">
+        <v>9</v>
+      </c>
+      <c r="D87" s="8">
         <v>3</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="10">
         <f t="shared" si="3"/>
         <v>0.22222222222222221</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87" s="9">
         <f t="shared" si="4"/>
         <v>0.7407407407407407</v>
       </c>
@@ -3232,23 +3369,23 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B88">
-        <v>9</v>
-      </c>
-      <c r="C88">
+      <c r="B88" s="8">
+        <v>9</v>
+      </c>
+      <c r="C88" s="7">
         <v>10</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="8">
         <v>2</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="10">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88" s="9">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
@@ -3258,23 +3395,23 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="8">
         <v>5</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="7">
         <v>11</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="8">
         <v>6</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="10">
         <f t="shared" si="3"/>
         <v>0.54545454545454541</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89" s="9">
         <f t="shared" si="4"/>
         <v>0.90909090909090895</v>
       </c>
@@ -3284,23 +3421,23 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="A90" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="8">
         <v>6</v>
       </c>
-      <c r="C90">
-        <v>9</v>
-      </c>
-      <c r="D90">
+      <c r="C90" s="7">
+        <v>9</v>
+      </c>
+      <c r="D90" s="8">
         <v>4</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="10">
         <f t="shared" si="3"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90" s="9">
         <f t="shared" si="4"/>
         <v>0.83333333333333326</v>
       </c>
@@ -3310,1063 +3447,1063 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="A91" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="8">
+        <v>6</v>
+      </c>
+      <c r="C91" s="7">
+        <v>7</v>
+      </c>
+      <c r="D91" s="8">
+        <v>1</v>
+      </c>
+      <c r="E91" s="10">
+        <f t="shared" si="3"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="F91" s="9">
+        <f t="shared" si="4"/>
+        <v>1.4285714285714284</v>
+      </c>
+      <c r="G91" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B92" s="8">
+        <v>3</v>
+      </c>
+      <c r="C92" s="7">
+        <v>10</v>
+      </c>
+      <c r="D92" s="8">
+        <v>7</v>
+      </c>
+      <c r="E92" s="10">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="F92" s="9">
+        <f t="shared" si="4"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="G92" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B93" s="8">
+        <v>7</v>
+      </c>
+      <c r="C93" s="7">
+        <v>12</v>
+      </c>
+      <c r="D93" s="8">
+        <v>5</v>
+      </c>
+      <c r="E93" s="10">
+        <f t="shared" si="3"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F93" s="9">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333348</v>
+      </c>
+      <c r="G93" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="8">
+        <v>9</v>
+      </c>
+      <c r="C94" s="7">
+        <v>9</v>
+      </c>
+      <c r="D94" s="8">
+        <v>2</v>
+      </c>
+      <c r="E94" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G94" t="str">
+        <f t="shared" si="5"/>
+        <v>Low Risk</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="8">
+        <v>4</v>
+      </c>
+      <c r="C95" s="7">
+        <v>13</v>
+      </c>
+      <c r="D95" s="8">
+        <v>9</v>
+      </c>
+      <c r="E95" s="10">
+        <f t="shared" si="3"/>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="F95" s="9">
+        <f t="shared" si="4"/>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="G95" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" s="8">
+        <v>6</v>
+      </c>
+      <c r="C96" s="7">
+        <v>10</v>
+      </c>
+      <c r="D96" s="8">
+        <v>3</v>
+      </c>
+      <c r="E96" s="10">
+        <f t="shared" si="3"/>
+        <v>0.4</v>
+      </c>
+      <c r="F96" s="9">
+        <f t="shared" si="4"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G96" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="8">
+        <v>5</v>
+      </c>
+      <c r="C97" s="7">
         <v>8</v>
       </c>
-      <c r="C91">
+      <c r="D97" s="8">
+        <v>1</v>
+      </c>
+      <c r="E97" s="10">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="F97" s="9">
+        <f t="shared" si="4"/>
+        <v>3.75</v>
+      </c>
+      <c r="G97" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B98" s="8">
+        <v>8</v>
+      </c>
+      <c r="C98" s="7">
+        <v>11</v>
+      </c>
+      <c r="D98" s="8">
+        <v>4</v>
+      </c>
+      <c r="E98" s="10">
+        <f t="shared" si="3"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="F98" s="9">
+        <f t="shared" si="4"/>
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="G98" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B99" s="8">
+        <v>3</v>
+      </c>
+      <c r="C99" s="7">
+        <v>9</v>
+      </c>
+      <c r="D99" s="8">
+        <v>6</v>
+      </c>
+      <c r="E99" s="10">
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F99" s="9">
+        <f t="shared" si="4"/>
+        <v>1.1111111111111112</v>
+      </c>
+      <c r="G99" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B100" s="8">
         <v>7</v>
       </c>
-      <c r="D91">
+      <c r="C100" s="7">
+        <v>10</v>
+      </c>
+      <c r="D100" s="8">
+        <v>2</v>
+      </c>
+      <c r="E100" s="10">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
+      <c r="F100" s="9">
+        <f t="shared" si="4"/>
+        <v>1.5</v>
+      </c>
+      <c r="G100" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" s="8">
+        <v>9</v>
+      </c>
+      <c r="C101" s="7">
+        <v>12</v>
+      </c>
+      <c r="D101" s="8">
+        <v>5</v>
+      </c>
+      <c r="E101" s="10">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F101" s="9">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="G101" t="str">
+        <f t="shared" si="5"/>
+        <v>Low Risk</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B102" s="8">
+        <v>4</v>
+      </c>
+      <c r="C102" s="7">
+        <v>8</v>
+      </c>
+      <c r="D102" s="8">
+        <v>3</v>
+      </c>
+      <c r="E102" s="10">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="F102" s="9">
+        <f t="shared" si="4"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="G102" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B103" s="8">
+        <v>6</v>
+      </c>
+      <c r="C103" s="7">
+        <v>14</v>
+      </c>
+      <c r="D103" s="8">
+        <v>10</v>
+      </c>
+      <c r="E103" s="10">
+        <f t="shared" si="3"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F103" s="9">
+        <f t="shared" si="4"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="G103" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" s="8">
+        <v>5</v>
+      </c>
+      <c r="C104" s="7">
+        <v>9</v>
+      </c>
+      <c r="D104" s="8">
+        <v>2</v>
+      </c>
+      <c r="E104" s="10">
+        <f t="shared" si="3"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="F104" s="9">
+        <f t="shared" si="4"/>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="G104" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B105" s="8">
+        <v>8</v>
+      </c>
+      <c r="C105" s="7">
+        <v>10</v>
+      </c>
+      <c r="D105" s="8">
+        <v>4</v>
+      </c>
+      <c r="E105" s="10">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="F105" s="9">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="G105" t="str">
+        <f t="shared" si="5"/>
+        <v>Low Risk</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" s="8">
+        <v>3</v>
+      </c>
+      <c r="C106" s="7">
+        <v>7</v>
+      </c>
+      <c r="D106" s="8">
         <v>1</v>
       </c>
-      <c r="E91" s="2">
-        <f t="shared" si="3"/>
-        <v>-0.14285714285714285</v>
-      </c>
-      <c r="F91" s="1">
-        <f t="shared" si="4"/>
-        <v>-1.4285714285714284</v>
-      </c>
-      <c r="G91" t="str">
+      <c r="E106" s="10">
+        <f t="shared" si="3"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="F106" s="9">
+        <f t="shared" si="4"/>
+        <v>5.7142857142857135</v>
+      </c>
+      <c r="G106" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" s="8">
+        <v>7</v>
+      </c>
+      <c r="C107" s="7">
+        <v>11</v>
+      </c>
+      <c r="D107" s="8">
+        <v>6</v>
+      </c>
+      <c r="E107" s="10">
+        <f t="shared" si="3"/>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="F107" s="9">
+        <f t="shared" si="4"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="G107" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B108" s="8">
+        <v>5</v>
+      </c>
+      <c r="C108" s="7">
+        <v>9</v>
+      </c>
+      <c r="D108" s="8">
+        <v>3</v>
+      </c>
+      <c r="E108" s="10">
+        <f t="shared" si="3"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="F108" s="9">
+        <f t="shared" si="4"/>
+        <v>1.4814814814814814</v>
+      </c>
+      <c r="G108" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B109" s="8">
+        <v>9</v>
+      </c>
+      <c r="C109" s="7">
+        <v>10</v>
+      </c>
+      <c r="D109" s="8">
+        <v>2</v>
+      </c>
+      <c r="E109" s="10">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
+      <c r="F109" s="9">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="G109" t="str">
         <f t="shared" si="5"/>
         <v>Low Risk</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>93</v>
-      </c>
-      <c r="B92">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="8">
+        <v>4</v>
+      </c>
+      <c r="C110" s="7">
+        <v>12</v>
+      </c>
+      <c r="D110" s="8">
+        <v>8</v>
+      </c>
+      <c r="E110" s="10">
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F110" s="9">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="G110" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B111" s="8">
+        <v>6</v>
+      </c>
+      <c r="C111" s="7">
+        <v>8</v>
+      </c>
+      <c r="D111" s="8">
+        <v>1</v>
+      </c>
+      <c r="E111" s="10">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="F111" s="9">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="G111" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" s="8">
+        <v>8</v>
+      </c>
+      <c r="C112" s="7">
+        <v>9</v>
+      </c>
+      <c r="D112" s="8">
+        <v>4</v>
+      </c>
+      <c r="E112" s="10">
+        <f t="shared" si="3"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F112" s="9">
+        <f t="shared" si="4"/>
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="G112" t="str">
+        <f t="shared" si="5"/>
+        <v>Low Risk</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="8">
         <v>3</v>
       </c>
-      <c r="C92">
+      <c r="C113" s="7">
         <v>10</v>
       </c>
-      <c r="D92">
+      <c r="D113" s="8">
         <v>7</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E113" s="10">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F113" s="9">
         <f t="shared" si="4"/>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G92" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>94</v>
-      </c>
-      <c r="B93">
+      <c r="G113" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="8">
         <v>7</v>
       </c>
-      <c r="C93">
+      <c r="C114" s="7">
+        <v>8</v>
+      </c>
+      <c r="D114" s="8">
+        <v>2</v>
+      </c>
+      <c r="E114" s="10">
+        <f t="shared" si="3"/>
+        <v>0.125</v>
+      </c>
+      <c r="F114" s="9">
+        <f t="shared" si="4"/>
+        <v>0.625</v>
+      </c>
+      <c r="G114" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" s="8">
+        <v>5</v>
+      </c>
+      <c r="C115" s="7">
+        <v>13</v>
+      </c>
+      <c r="D115" s="8">
+        <v>9</v>
+      </c>
+      <c r="E115" s="10">
+        <f t="shared" si="3"/>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="F115" s="9">
+        <f t="shared" si="4"/>
+        <v>0.68376068376068377</v>
+      </c>
+      <c r="G115" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" s="8">
+        <v>9</v>
+      </c>
+      <c r="C116" s="7">
+        <v>9</v>
+      </c>
+      <c r="D116" s="8">
+        <v>1</v>
+      </c>
+      <c r="E116" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G116" t="str">
+        <f t="shared" si="5"/>
+        <v>Low Risk</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" s="8">
+        <v>4</v>
+      </c>
+      <c r="C117" s="7">
+        <v>11</v>
+      </c>
+      <c r="D117" s="8">
+        <v>5</v>
+      </c>
+      <c r="E117" s="10">
+        <f t="shared" si="3"/>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="F117" s="9">
+        <f t="shared" si="4"/>
+        <v>1.2727272727272725</v>
+      </c>
+      <c r="G117" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" s="8">
+        <v>6</v>
+      </c>
+      <c r="C118" s="7">
+        <v>10</v>
+      </c>
+      <c r="D118" s="8">
+        <v>3</v>
+      </c>
+      <c r="E118" s="10">
+        <f t="shared" si="3"/>
+        <v>0.4</v>
+      </c>
+      <c r="F118" s="9">
+        <f t="shared" si="4"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G118" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="8">
+        <v>8</v>
+      </c>
+      <c r="C119" s="7">
         <v>12</v>
       </c>
-      <c r="D93">
+      <c r="D119" s="8">
+        <v>6</v>
+      </c>
+      <c r="E119" s="10">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F119" s="9">
+        <f t="shared" si="4"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="G119" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" s="8">
+        <v>3</v>
+      </c>
+      <c r="C120" s="7">
+        <v>9</v>
+      </c>
+      <c r="D120" s="8">
+        <v>2</v>
+      </c>
+      <c r="E120" s="10">
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F120" s="9">
+        <f t="shared" si="4"/>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="G120" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="8">
+        <v>7</v>
+      </c>
+      <c r="C121" s="7">
+        <v>10</v>
+      </c>
+      <c r="D121" s="8">
+        <v>4</v>
+      </c>
+      <c r="E121" s="10">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
+      <c r="F121" s="9">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
+      </c>
+      <c r="G121" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" s="8">
         <v>5</v>
       </c>
-      <c r="E93" s="2">
+      <c r="C122" s="7">
+        <v>8</v>
+      </c>
+      <c r="D122" s="8">
+        <v>1</v>
+      </c>
+      <c r="E122" s="10">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="F122" s="9">
+        <f t="shared" si="4"/>
+        <v>3.75</v>
+      </c>
+      <c r="G122" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="8">
+        <v>9</v>
+      </c>
+      <c r="C123" s="7">
+        <v>14</v>
+      </c>
+      <c r="D123" s="8">
+        <v>8</v>
+      </c>
+      <c r="E123" s="10">
+        <f t="shared" si="3"/>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="F123" s="9">
+        <f t="shared" si="4"/>
+        <v>0.44642857142857145</v>
+      </c>
+      <c r="G123" t="str">
+        <f t="shared" si="5"/>
+        <v>Low Risk</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" s="8">
+        <v>4</v>
+      </c>
+      <c r="C124" s="7">
+        <v>9</v>
+      </c>
+      <c r="D124" s="8">
+        <v>3</v>
+      </c>
+      <c r="E124" s="10">
+        <f t="shared" si="3"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="F124" s="9">
+        <f t="shared" si="4"/>
+        <v>1.8518518518518521</v>
+      </c>
+      <c r="G124" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" s="8">
+        <v>6</v>
+      </c>
+      <c r="C125" s="7">
+        <v>11</v>
+      </c>
+      <c r="D125" s="8">
+        <v>5</v>
+      </c>
+      <c r="E125" s="10">
+        <f t="shared" si="3"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="F125" s="9">
+        <f t="shared" si="4"/>
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="G125" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" s="8">
+        <v>8</v>
+      </c>
+      <c r="C126" s="7">
+        <v>10</v>
+      </c>
+      <c r="D126" s="8">
+        <v>2</v>
+      </c>
+      <c r="E126" s="10">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="F126" s="9">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G126" t="str">
+        <f t="shared" si="5"/>
+        <v>Medium Risk</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="8">
+        <v>3</v>
+      </c>
+      <c r="C127" s="7">
+        <v>9</v>
+      </c>
+      <c r="D127" s="8">
+        <v>6</v>
+      </c>
+      <c r="E127" s="10">
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F127" s="9">
+        <f t="shared" si="4"/>
+        <v>1.1111111111111112</v>
+      </c>
+      <c r="G127" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" s="8">
+        <v>7</v>
+      </c>
+      <c r="C128" s="7">
+        <v>12</v>
+      </c>
+      <c r="D128" s="8">
+        <v>4</v>
+      </c>
+      <c r="E128" s="10">
         <f t="shared" si="3"/>
         <v>0.41666666666666669</v>
       </c>
-      <c r="F93" s="1">
-        <f t="shared" si="4"/>
-        <v>0.83333333333333348</v>
-      </c>
-      <c r="G93" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>95</v>
-      </c>
-      <c r="B94">
-        <v>9</v>
-      </c>
-      <c r="C94">
-        <v>9</v>
-      </c>
-      <c r="D94">
+      <c r="F128" s="9">
+        <f t="shared" si="4"/>
+        <v>1.0416666666666667</v>
+      </c>
+      <c r="G128" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" s="8">
+        <v>5</v>
+      </c>
+      <c r="C129" s="7">
+        <v>8</v>
+      </c>
+      <c r="D129" s="8">
+        <v>1</v>
+      </c>
+      <c r="E129" s="10">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="F129" s="9">
+        <f t="shared" si="4"/>
+        <v>3.75</v>
+      </c>
+      <c r="G129" t="str">
+        <f t="shared" si="5"/>
+        <v>High Risk</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130" s="8">
+        <v>9</v>
+      </c>
+      <c r="C130" s="7">
+        <v>13</v>
+      </c>
+      <c r="D130" s="8">
+        <v>7</v>
+      </c>
+      <c r="E130" s="10">
+        <f t="shared" si="3"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="F130" s="9">
+        <f t="shared" si="4"/>
+        <v>0.43956043956043961</v>
+      </c>
+      <c r="G130" t="str">
+        <f t="shared" si="5"/>
+        <v>Low Risk</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B131" s="8">
+        <v>6</v>
+      </c>
+      <c r="C131" s="7">
+        <v>9</v>
+      </c>
+      <c r="D131" s="8">
         <v>2</v>
       </c>
-      <c r="E94" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F94" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G94" t="str">
-        <f t="shared" si="5"/>
-        <v>Low Risk</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>96</v>
-      </c>
-      <c r="B95">
-        <v>4</v>
-      </c>
-      <c r="C95">
-        <v>13</v>
-      </c>
-      <c r="D95">
-        <v>9</v>
-      </c>
-      <c r="E95" s="2">
-        <f t="shared" si="3"/>
-        <v>0.69230769230769229</v>
-      </c>
-      <c r="F95" s="1">
-        <f t="shared" si="4"/>
-        <v>0.76923076923076927</v>
-      </c>
-      <c r="G95" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>97</v>
-      </c>
-      <c r="B96">
-        <v>6</v>
-      </c>
-      <c r="C96">
-        <v>10</v>
-      </c>
-      <c r="D96">
-        <v>3</v>
-      </c>
-      <c r="E96" s="2">
-        <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="F96" s="1">
-        <f t="shared" si="4"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="G96" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>98</v>
-      </c>
-      <c r="B97">
-        <v>5</v>
-      </c>
-      <c r="C97">
-        <v>8</v>
-      </c>
-      <c r="D97">
-        <v>1</v>
-      </c>
-      <c r="E97" s="2">
-        <f t="shared" si="3"/>
-        <v>0.375</v>
-      </c>
-      <c r="F97" s="1">
-        <f t="shared" si="4"/>
-        <v>3.75</v>
-      </c>
-      <c r="G97" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>99</v>
-      </c>
-      <c r="B98">
-        <v>8</v>
-      </c>
-      <c r="C98">
-        <v>11</v>
-      </c>
-      <c r="D98">
-        <v>4</v>
-      </c>
-      <c r="E98" s="2">
-        <f t="shared" si="3"/>
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="F98" s="1">
-        <f t="shared" si="4"/>
-        <v>0.68181818181818177</v>
-      </c>
-      <c r="G98" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>100</v>
-      </c>
-      <c r="B99">
-        <v>3</v>
-      </c>
-      <c r="C99">
-        <v>9</v>
-      </c>
-      <c r="D99">
-        <v>6</v>
-      </c>
-      <c r="E99" s="2">
-        <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F99" s="1">
-        <f t="shared" si="4"/>
-        <v>1.1111111111111112</v>
-      </c>
-      <c r="G99" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>101</v>
-      </c>
-      <c r="B100">
-        <v>7</v>
-      </c>
-      <c r="C100">
-        <v>10</v>
-      </c>
-      <c r="D100">
-        <v>2</v>
-      </c>
-      <c r="E100" s="2">
-        <f t="shared" si="3"/>
-        <v>0.3</v>
-      </c>
-      <c r="F100" s="1">
-        <f t="shared" si="4"/>
-        <v>1.5</v>
-      </c>
-      <c r="G100" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>102</v>
-      </c>
-      <c r="B101">
-        <v>9</v>
-      </c>
-      <c r="C101">
-        <v>12</v>
-      </c>
-      <c r="D101">
-        <v>5</v>
-      </c>
-      <c r="E101" s="2">
-        <f t="shared" si="3"/>
-        <v>0.25</v>
-      </c>
-      <c r="F101" s="1">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="G101" t="str">
-        <f t="shared" si="5"/>
-        <v>Low Risk</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>103</v>
-      </c>
-      <c r="B102">
-        <v>4</v>
-      </c>
-      <c r="C102">
-        <v>8</v>
-      </c>
-      <c r="D102">
-        <v>3</v>
-      </c>
-      <c r="E102" s="2">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="F102" s="1">
-        <f t="shared" si="4"/>
-        <v>1.6666666666666665</v>
-      </c>
-      <c r="G102" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>104</v>
-      </c>
-      <c r="B103">
-        <v>6</v>
-      </c>
-      <c r="C103">
-        <v>14</v>
-      </c>
-      <c r="D103">
-        <v>10</v>
-      </c>
-      <c r="E103" s="2">
-        <f t="shared" si="3"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="F103" s="1">
-        <f t="shared" si="4"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="G103" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>105</v>
-      </c>
-      <c r="B104">
-        <v>5</v>
-      </c>
-      <c r="C104">
-        <v>9</v>
-      </c>
-      <c r="D104">
-        <v>2</v>
-      </c>
-      <c r="E104" s="2">
-        <f t="shared" si="3"/>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="F104" s="1">
-        <f t="shared" si="4"/>
-        <v>2.2222222222222223</v>
-      </c>
-      <c r="G104" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>106</v>
-      </c>
-      <c r="B105">
-        <v>8</v>
-      </c>
-      <c r="C105">
-        <v>10</v>
-      </c>
-      <c r="D105">
-        <v>4</v>
-      </c>
-      <c r="E105" s="2">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="F105" s="1">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="G105" t="str">
-        <f t="shared" si="5"/>
-        <v>Low Risk</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>107</v>
-      </c>
-      <c r="B106">
-        <v>3</v>
-      </c>
-      <c r="C106">
-        <v>7</v>
-      </c>
-      <c r="D106">
-        <v>1</v>
-      </c>
-      <c r="E106" s="2">
-        <f t="shared" si="3"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="F106" s="1">
-        <f t="shared" si="4"/>
-        <v>5.7142857142857135</v>
-      </c>
-      <c r="G106" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>108</v>
-      </c>
-      <c r="B107">
-        <v>7</v>
-      </c>
-      <c r="C107">
-        <v>11</v>
-      </c>
-      <c r="D107">
-        <v>6</v>
-      </c>
-      <c r="E107" s="2">
-        <f t="shared" si="3"/>
-        <v>0.36363636363636365</v>
-      </c>
-      <c r="F107" s="1">
-        <f t="shared" si="4"/>
-        <v>0.60606060606060608</v>
-      </c>
-      <c r="G107" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>109</v>
-      </c>
-      <c r="B108">
-        <v>5</v>
-      </c>
-      <c r="C108">
-        <v>9</v>
-      </c>
-      <c r="D108">
-        <v>3</v>
-      </c>
-      <c r="E108" s="2">
-        <f t="shared" si="3"/>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="F108" s="1">
-        <f t="shared" si="4"/>
-        <v>1.4814814814814814</v>
-      </c>
-      <c r="G108" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>110</v>
-      </c>
-      <c r="B109">
-        <v>9</v>
-      </c>
-      <c r="C109">
-        <v>10</v>
-      </c>
-      <c r="D109">
-        <v>2</v>
-      </c>
-      <c r="E109" s="2">
-        <f t="shared" si="3"/>
-        <v>0.1</v>
-      </c>
-      <c r="F109" s="1">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="G109" t="str">
-        <f t="shared" si="5"/>
-        <v>Low Risk</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>111</v>
-      </c>
-      <c r="B110">
-        <v>4</v>
-      </c>
-      <c r="C110">
-        <v>12</v>
-      </c>
-      <c r="D110">
-        <v>8</v>
-      </c>
-      <c r="E110" s="2">
-        <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F110" s="1">
-        <f t="shared" si="4"/>
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="G110" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>112</v>
-      </c>
-      <c r="B111">
-        <v>6</v>
-      </c>
-      <c r="C111">
-        <v>8</v>
-      </c>
-      <c r="D111">
-        <v>1</v>
-      </c>
-      <c r="E111" s="2">
-        <f t="shared" si="3"/>
-        <v>0.25</v>
-      </c>
-      <c r="F111" s="1">
-        <f t="shared" si="4"/>
-        <v>2.5</v>
-      </c>
-      <c r="G111" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>113</v>
-      </c>
-      <c r="B112">
-        <v>8</v>
-      </c>
-      <c r="C112">
-        <v>9</v>
-      </c>
-      <c r="D112">
-        <v>4</v>
-      </c>
-      <c r="E112" s="2">
-        <f t="shared" si="3"/>
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="F112" s="1">
-        <f t="shared" si="4"/>
-        <v>0.27777777777777779</v>
-      </c>
-      <c r="G112" t="str">
-        <f t="shared" si="5"/>
-        <v>Low Risk</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>114</v>
-      </c>
-      <c r="B113">
-        <v>3</v>
-      </c>
-      <c r="C113">
-        <v>10</v>
-      </c>
-      <c r="D113">
-        <v>7</v>
-      </c>
-      <c r="E113" s="2">
-        <f t="shared" si="3"/>
-        <v>0.7</v>
-      </c>
-      <c r="F113" s="1">
-        <f t="shared" si="4"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="G113" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>115</v>
-      </c>
-      <c r="B114">
-        <v>7</v>
-      </c>
-      <c r="C114">
-        <v>8</v>
-      </c>
-      <c r="D114">
-        <v>2</v>
-      </c>
-      <c r="E114" s="2">
-        <f t="shared" si="3"/>
-        <v>0.125</v>
-      </c>
-      <c r="F114" s="1">
-        <f t="shared" si="4"/>
-        <v>0.625</v>
-      </c>
-      <c r="G114" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>116</v>
-      </c>
-      <c r="B115">
-        <v>5</v>
-      </c>
-      <c r="C115">
-        <v>13</v>
-      </c>
-      <c r="D115">
-        <v>9</v>
-      </c>
-      <c r="E115" s="2">
-        <f t="shared" si="3"/>
-        <v>0.61538461538461542</v>
-      </c>
-      <c r="F115" s="1">
-        <f t="shared" si="4"/>
-        <v>0.68376068376068377</v>
-      </c>
-      <c r="G115" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>117</v>
-      </c>
-      <c r="B116">
-        <v>9</v>
-      </c>
-      <c r="C116">
-        <v>9</v>
-      </c>
-      <c r="D116">
-        <v>1</v>
-      </c>
-      <c r="E116" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F116" s="1">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G116" t="str">
-        <f t="shared" si="5"/>
-        <v>Low Risk</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>118</v>
-      </c>
-      <c r="B117">
-        <v>4</v>
-      </c>
-      <c r="C117">
-        <v>11</v>
-      </c>
-      <c r="D117">
-        <v>5</v>
-      </c>
-      <c r="E117" s="2">
-        <f t="shared" si="3"/>
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="F117" s="1">
-        <f t="shared" si="4"/>
-        <v>1.2727272727272725</v>
-      </c>
-      <c r="G117" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>119</v>
-      </c>
-      <c r="B118">
-        <v>6</v>
-      </c>
-      <c r="C118">
-        <v>10</v>
-      </c>
-      <c r="D118">
-        <v>3</v>
-      </c>
-      <c r="E118" s="2">
-        <f t="shared" si="3"/>
-        <v>0.4</v>
-      </c>
-      <c r="F118" s="1">
-        <f t="shared" si="4"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="G118" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>120</v>
-      </c>
-      <c r="B119">
-        <v>8</v>
-      </c>
-      <c r="C119">
-        <v>12</v>
-      </c>
-      <c r="D119">
-        <v>6</v>
-      </c>
-      <c r="E119" s="2">
+      <c r="E131" s="10">
         <f t="shared" si="3"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F119" s="1">
-        <f t="shared" si="4"/>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="G119" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>121</v>
-      </c>
-      <c r="B120">
-        <v>3</v>
-      </c>
-      <c r="C120">
-        <v>9</v>
-      </c>
-      <c r="D120">
-        <v>2</v>
-      </c>
-      <c r="E120" s="2">
-        <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F120" s="1">
-        <f t="shared" si="4"/>
-        <v>3.333333333333333</v>
-      </c>
-      <c r="G120" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>122</v>
-      </c>
-      <c r="B121">
-        <v>7</v>
-      </c>
-      <c r="C121">
-        <v>10</v>
-      </c>
-      <c r="D121">
-        <v>4</v>
-      </c>
-      <c r="E121" s="2">
-        <f t="shared" si="3"/>
-        <v>0.3</v>
-      </c>
-      <c r="F121" s="1">
-        <f t="shared" si="4"/>
-        <v>0.75</v>
-      </c>
-      <c r="G121" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>123</v>
-      </c>
-      <c r="B122">
-        <v>5</v>
-      </c>
-      <c r="C122">
-        <v>8</v>
-      </c>
-      <c r="D122">
-        <v>1</v>
-      </c>
-      <c r="E122" s="2">
-        <f t="shared" si="3"/>
-        <v>0.375</v>
-      </c>
-      <c r="F122" s="1">
-        <f t="shared" si="4"/>
-        <v>3.75</v>
-      </c>
-      <c r="G122" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>124</v>
-      </c>
-      <c r="B123">
-        <v>9</v>
-      </c>
-      <c r="C123">
-        <v>14</v>
-      </c>
-      <c r="D123">
-        <v>8</v>
-      </c>
-      <c r="E123" s="2">
-        <f t="shared" si="3"/>
-        <v>0.35714285714285715</v>
-      </c>
-      <c r="F123" s="1">
-        <f t="shared" si="4"/>
-        <v>0.44642857142857145</v>
-      </c>
-      <c r="G123" t="str">
-        <f t="shared" si="5"/>
-        <v>Low Risk</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>125</v>
-      </c>
-      <c r="B124">
-        <v>4</v>
-      </c>
-      <c r="C124">
-        <v>9</v>
-      </c>
-      <c r="D124">
-        <v>3</v>
-      </c>
-      <c r="E124" s="2">
-        <f t="shared" si="3"/>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="F124" s="1">
-        <f t="shared" si="4"/>
-        <v>1.8518518518518521</v>
-      </c>
-      <c r="G124" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>126</v>
-      </c>
-      <c r="B125">
-        <v>6</v>
-      </c>
-      <c r="C125">
-        <v>11</v>
-      </c>
-      <c r="D125">
-        <v>5</v>
-      </c>
-      <c r="E125" s="2">
-        <f t="shared" si="3"/>
-        <v>0.45454545454545453</v>
-      </c>
-      <c r="F125" s="1">
-        <f t="shared" si="4"/>
-        <v>0.90909090909090917</v>
-      </c>
-      <c r="G125" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>127</v>
-      </c>
-      <c r="B126">
-        <v>8</v>
-      </c>
-      <c r="C126">
-        <v>10</v>
-      </c>
-      <c r="D126">
-        <v>2</v>
-      </c>
-      <c r="E126" s="2">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="F126" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G126" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium Risk</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>128</v>
-      </c>
-      <c r="B127">
-        <v>3</v>
-      </c>
-      <c r="C127">
-        <v>9</v>
-      </c>
-      <c r="D127">
-        <v>6</v>
-      </c>
-      <c r="E127" s="2">
-        <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F127" s="1">
-        <f t="shared" si="4"/>
-        <v>1.1111111111111112</v>
-      </c>
-      <c r="G127" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>129</v>
-      </c>
-      <c r="B128">
-        <v>7</v>
-      </c>
-      <c r="C128">
-        <v>12</v>
-      </c>
-      <c r="D128">
-        <v>4</v>
-      </c>
-      <c r="E128" s="2">
-        <f t="shared" si="3"/>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F128" s="1">
-        <f t="shared" si="4"/>
-        <v>1.0416666666666667</v>
-      </c>
-      <c r="G128" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>130</v>
-      </c>
-      <c r="B129">
-        <v>5</v>
-      </c>
-      <c r="C129">
-        <v>8</v>
-      </c>
-      <c r="D129">
-        <v>1</v>
-      </c>
-      <c r="E129" s="2">
-        <f t="shared" si="3"/>
-        <v>0.375</v>
-      </c>
-      <c r="F129" s="1">
-        <f t="shared" si="4"/>
-        <v>3.75</v>
-      </c>
-      <c r="G129" t="str">
-        <f t="shared" si="5"/>
-        <v>High Risk</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>131</v>
-      </c>
-      <c r="B130">
-        <v>9</v>
-      </c>
-      <c r="C130">
-        <v>13</v>
-      </c>
-      <c r="D130">
-        <v>7</v>
-      </c>
-      <c r="E130" s="2">
-        <f t="shared" si="3"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="F130" s="1">
-        <f t="shared" si="4"/>
-        <v>0.43956043956043961</v>
-      </c>
-      <c r="G130" t="str">
-        <f t="shared" si="5"/>
-        <v>Low Risk</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>132</v>
-      </c>
-      <c r="B131">
-        <v>6</v>
-      </c>
-      <c r="C131">
-        <v>9</v>
-      </c>
-      <c r="D131">
-        <v>2</v>
-      </c>
-      <c r="E131" s="2">
-        <f t="shared" si="3"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="F131" s="1">
+      <c r="F131" s="9">
         <f t="shared" si="4"/>
         <v>1.6666666666666665</v>
       </c>
@@ -4379,32 +4516,32 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G131">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="HIgh Risk">
-      <formula>NOT(ISERROR(SEARCH("HIgh Risk",G8)))</formula>
+  <conditionalFormatting sqref="G7:G131">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="HIgh Risk">
+      <formula>NOT(ISERROR(SEARCH("HIgh Risk",G7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Low Risk">
-      <formula>NOT(ISERROR(SEARCH("Low Risk",G8)))</formula>
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Low Risk">
+      <formula>NOT(ISERROR(SEARCH("Low Risk",G7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="Medium Risk">
-      <formula>NOT(ISERROR(SEARCH("Medium Risk",G8)))</formula>
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Medium Risk">
+      <formula>NOT(ISERROR(SEARCH("Medium Risk",G7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="High Risk">
-      <formula>NOT(ISERROR(SEARCH("High Risk",G8)))</formula>
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="High Risk">
+      <formula>NOT(ISERROR(SEARCH("High Risk",G7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="HIgh Risk">
-      <formula>NOT(ISERROR(SEARCH("HIgh Risk",G7)))</formula>
+  <conditionalFormatting sqref="G8:G131">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"High Risk"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Low Risk">
-      <formula>NOT(ISERROR(SEARCH("Low Risk",G7)))</formula>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Medium Risk"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Medium Risk">
-      <formula>NOT(ISERROR(SEARCH("Medium Risk",G7)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"High Risk"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="High Risk">
-      <formula>NOT(ISERROR(SEARCH("High Risk",G7)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Low Risk"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
